--- a/ERP Report/PICS/Sr.Super60_Nucleus(Adv)/P2/K.xlsx
+++ b/ERP Report/PICS/Sr.Super60_Nucleus(Adv)/P2/K.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SRINIVASU(BNG11531)\ECITY\SNAPSHOT 2026-2027\Sr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E660E32-8131-4285-8357-40CF194E8814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAC529A-4D2A-464D-87EF-9F46D063A72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="600" windowWidth="20370" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KEY" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>Q_No</t>
   </si>
@@ -28,31 +28,16 @@
     <t>Key</t>
   </si>
   <si>
-    <t>BCD</t>
+    <t>B</t>
   </si>
   <si>
-    <t>ABD</t>
+    <t>AB</t>
   </si>
   <si>
     <t>AC</t>
   </si>
   <si>
-    <t>BC</t>
-  </si>
-  <si>
-    <t>11.86-11.87</t>
-  </si>
-  <si>
-    <t>1.89-1.90</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
+    <t>ABCD</t>
   </si>
   <si>
     <t>BD</t>
@@ -61,16 +46,28 @@
     <t>ABC</t>
   </si>
   <si>
+    <t>BC</t>
+  </si>
+  <si>
     <t>CD</t>
   </si>
   <si>
-    <t>0.29-0.30</t>
+    <t>AD</t>
   </si>
   <si>
-    <t>D</t>
+    <t>2.8-2.91</t>
   </si>
   <si>
-    <t>ABCD</t>
+    <t>4.55-4.75</t>
+  </si>
+  <si>
+    <t>379-380</t>
+  </si>
+  <si>
+    <t>15.08-15.10</t>
+  </si>
+  <si>
+    <t>0.38-0.38</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="1"/>
@@ -1114,23 +1111,23 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
+      <c r="B2" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
+      <c r="B3" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="2">
         <v>4</v>
       </c>
     </row>
@@ -1138,56 +1135,56 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>2</v>
+      <c r="B5" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
+      <c r="B6" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
+      <c r="B7" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
-        <v>40</v>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
-        <v>204</v>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
-        <v>21</v>
+      <c r="B10" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
-        <v>20</v>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -1195,7 +1192,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1210,32 +1207,32 @@
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>8</v>
+      <c r="B14" s="2">
+        <v>1.77</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>8</v>
+      <c r="B15" s="2">
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>9</v>
+      <c r="B16" s="2">
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>10</v>
+      <c r="B17" s="2">
+        <v>0.25</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -1243,7 +1240,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -1251,7 +1248,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>9</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -1259,47 +1256,47 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>3</v>
+      <c r="B21" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>4</v>
+      <c r="B22" s="2">
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>11</v>
+      <c r="B23" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>12</v>
+      <c r="B24" s="2">
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>13</v>
+      <c r="B25" s="2">
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -1307,55 +1304,55 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
-        <v>11</v>
+      <c r="B27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
-        <v>60</v>
+      <c r="B28" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
-        <v>1</v>
+      <c r="B29" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="2">
-        <v>9</v>
+      <c r="B30" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
-        <v>118</v>
+      <c r="B31" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>14</v>
+      <c r="B32" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -1363,15 +1360,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>10</v>
+      <c r="B34" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -1379,23 +1376,23 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>10</v>
+      <c r="B36" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="2">
-        <v>4</v>
+      <c r="B37" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -1403,7 +1400,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -1411,39 +1408,39 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>16</v>
+      <c r="B40" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>4</v>
+      <c r="B41" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>12</v>
+      <c r="B42" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>4</v>
+      <c r="B43" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -1451,7 +1448,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
@@ -1459,30 +1456,30 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="2">
-        <v>2</v>
+      <c r="B46" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="2">
-        <v>1</v>
+      <c r="B47" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1490,80 +1487,56 @@
       <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="2">
-        <v>24</v>
+      <c r="B49" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="2">
-        <v>3</v>
+      <c r="B50" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="2">
-        <v>0.5</v>
+      <c r="B51" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>8</v>
+      <c r="B52" s="2">
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>9</v>
+      <c r="B53" s="2">
+        <v>7.2</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>10</v>
+      <c r="B54" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="1">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2">
+      <c r="B55" s="2">
         <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="1">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="1">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
